--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saido\Documents\eps-indonesia-cpl\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="2670" windowWidth="25665" windowHeight="13515" tabRatio="698"/>
+    <workbookView xWindow="2070" yWindow="2670" windowWidth="25665" windowHeight="13515" tabRatio="698" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="GRA-ntnldebtinterest" sheetId="15" r:id="rId10"/>
     <sheet name="GRA-remainder" sheetId="16" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -272,7 +272,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,7 +388,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -715,17 +715,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="80.86328125" customWidth="1"/>
+    <col min="2" max="2" width="80.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,72 +733,72 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -806,7 +806,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2</v>
       </c>
@@ -814,7 +814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>4</v>
       </c>
@@ -830,7 +830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>5</v>
       </c>
@@ -838,114 +838,114 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B41" s="13"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -962,12 +962,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -975,7 +975,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -984,7 +984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1027,12 +1027,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1040,16 +1040,16 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2">
         <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B16:F16)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1092,33 +1092,33 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1128,7 +1128,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>46</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1162,13 +1162,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1308,12 +1308,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>52</v>
       </c>
@@ -1338,12 +1338,12 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>46</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C22" s="10">
         <f t="shared" ref="C22:F22" si="0">IFERROR(C8/SUM($B8:$F8),1/COUNT($B8:$F8))</f>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="10">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="F22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1563,21 +1563,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="10">
         <f t="shared" ref="B30:F30" si="8">IFERROR(B16/SUM($B16:$F16),1/COUNT($B16:$F16))</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="8"/>
@@ -1601,12 +1601,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1639,15 +1639,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
       <c r="B5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1666,12 +1666,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1731,12 +1731,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1796,12 +1796,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1861,12 +1861,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1926,12 +1926,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1991,12 +1991,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.86328125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
